--- a/documents/Lifespans in the Bible.xlsx
+++ b/documents/Lifespans in the Bible.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author>Unknown Author</author>
   </authors>
@@ -37,6 +37,27 @@
           <t xml:space="preserve">In the year 1656, the last year of Methuselah’s life, the flood occurred which drastically changed the earth</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>14</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="A10" authorId="0">
       <text>
@@ -49,6 +70,27 @@
           <t xml:space="preserve">Lamech died 5 years before the flood.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>3</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="A11" authorId="0">
       <text>
@@ -61,6 +103,27 @@
           <t xml:space="preserve">Noah lived for 600 years before the flood and 350 years after the flood.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>11</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="A13" authorId="0">
       <text>
@@ -73,6 +136,27 @@
           <t xml:space="preserve">Arphaxad was the first recorded man to live entirely after the flood. He was born 2 years after the flood (Gen 11:10).</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>15</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
   </commentList>
 </comments>
@@ -754,10 +838,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0207393334916489"/>
-          <c:y val="0.00867338028988882"/>
-          <c:w val="0.972690572310615"/>
-          <c:h val="0.840386518423657"/>
+          <c:x val="0.0207398807324925"/>
+          <c:y val="0.00867388520200256"/>
+          <c:w val="0.972663465090506"/>
+          <c:h val="0.840319012690651"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -792,7 +876,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -1141,11 +1225,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="40067169"/>
-        <c:axId val="30896679"/>
+        <c:axId val="36003860"/>
+        <c:axId val="90724175"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="40067169"/>
+        <c:axId val="36003860"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1158,7 +1242,7 @@
         <c:spPr>
           <a:ln w="0">
             <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
+              <a:srgbClr val="B3B3B3"/>
             </a:solidFill>
           </a:ln>
         </c:spPr>
@@ -1167,7 +1251,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="600" strike="noStrike" u="none">
+              <a:defRPr sz="600" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1178,7 +1262,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30896679"/>
+        <c:crossAx val="90724175"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1186,7 +1270,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="30896679"/>
+        <c:axId val="90724175"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1196,7 +1280,7 @@
           <c:spPr>
             <a:ln w="0">
               <a:solidFill>
-                <a:srgbClr val="b3b3b3"/>
+                <a:srgbClr val="B3B3B3"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
@@ -1205,7 +1289,7 @@
           <c:spPr>
             <a:ln w="0">
               <a:solidFill>
-                <a:srgbClr val="dddddd"/>
+                <a:srgbClr val="DDDDDD"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
@@ -1217,7 +1301,7 @@
         <c:spPr>
           <a:ln w="0">
             <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
+              <a:srgbClr val="B3B3B3"/>
             </a:solidFill>
           </a:ln>
         </c:spPr>
@@ -1226,7 +1310,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="600" strike="noStrike" u="none">
+              <a:defRPr sz="600" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1237,7 +1321,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40067169"/>
+        <c:crossAx val="36003860"/>
         <c:crossesAt val="1"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="50"/>
@@ -1246,7 +1330,7 @@
         <a:noFill/>
         <a:ln w="0">
           <a:solidFill>
-            <a:srgbClr val="b3b3b3"/>
+            <a:srgbClr val="B3B3B3"/>
           </a:solidFill>
         </a:ln>
       </c:spPr>
@@ -1256,13 +1340,229 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="0">
       <a:noFill/>
     </a:ln>
   </c:spPr>
 </c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarkerLayout>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1276,9 +1576,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>666360</xdr:colOff>
+      <xdr:colOff>666000</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>29880</xdr:rowOff>
+      <xdr:rowOff>29520</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1287,7 +1587,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="38160" y="23040"/>
-        <a:ext cx="13643280" cy="6184080"/>
+        <a:ext cx="13642920" cy="6183720"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1325,7 +1625,7 @@
         </a:prstGeom>
         <a:ln w="0">
           <a:solidFill>
-            <a:srgbClr val="ff0000"/>
+            <a:srgbClr val="FF0000"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
@@ -1336,7 +1636,7 @@
         <a:fontRef idx="minor"/>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr lIns="0" rIns="0" tIns="0" bIns="0" anchor="ctr" anchorCtr="1">
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1">
           <a:noAutofit/>
         </a:bodyPr>
         <a:p>
@@ -1346,7 +1646,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="en-US" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
@@ -1357,7 +1657,7 @@
             </a:rPr>
             <a:t>Flood</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="en-US" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -1369,7 +1669,7 @@
               <a:spcPct val="100000"/>
             </a:lnSpc>
           </a:pPr>
-          <a:endParaRPr b="0" lang="en-US" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="en-US" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -1418,7 +1718,7 @@
         <a:fontRef idx="minor"/>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr lIns="0" rIns="0" tIns="0" bIns="0" anchor="ctr" anchorCtr="1">
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1">
           <a:noAutofit/>
         </a:bodyPr>
         <a:p>
@@ -1428,7 +1728,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="en-US" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
@@ -1439,7 +1739,7 @@
             </a:rPr>
             <a:t>First recorded man to live entirely after the flood</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="en-US" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -1451,7 +1751,7 @@
               <a:spcPct val="100000"/>
             </a:lnSpc>
           </a:pPr>
-          <a:endParaRPr b="0" lang="en-US" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="en-US" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -1472,37 +1772,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -2166,7 +2466,7 @@
       <c r="D33" s="10"/>
       <c r="F33" s="10"/>
     </row>
-    <row r="34" customFormat="false" ht="67.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="69.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>80</v>
       </c>
@@ -2179,7 +2479,7 @@
       <c r="D34" s="10"/>
       <c r="F34" s="10"/>
     </row>
-    <row r="35" customFormat="false" ht="67.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="69.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>82</v>
       </c>
@@ -2205,7 +2505,7 @@
       <c r="D36" s="10"/>
       <c r="F36" s="10"/>
     </row>
-    <row r="37" customFormat="false" ht="27.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="27.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>86</v>
       </c>
@@ -2231,7 +2531,7 @@
       <c r="D38" s="10"/>
       <c r="F38" s="10"/>
     </row>
-    <row r="39" customFormat="false" ht="67.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="69.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>90</v>
       </c>
@@ -2270,7 +2570,7 @@
       <c r="D41" s="10"/>
       <c r="F41" s="10"/>
     </row>
-    <row r="42" customFormat="false" ht="67.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="69.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>96</v>
       </c>
@@ -2283,7 +2583,7 @@
       <c r="D42" s="10"/>
       <c r="F42" s="10"/>
     </row>
-    <row r="43" customFormat="false" ht="67.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="69.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>98</v>
       </c>
@@ -2296,7 +2596,7 @@
       <c r="D43" s="10"/>
       <c r="F43" s="10"/>
     </row>
-    <row r="44" customFormat="false" ht="67.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="69.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>100</v>
       </c>
@@ -2322,7 +2622,7 @@
       <c r="D45" s="10"/>
       <c r="F45" s="10"/>
     </row>
-    <row r="46" customFormat="false" ht="67.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="69.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>104</v>
       </c>
@@ -2335,7 +2635,7 @@
       <c r="D46" s="10"/>
       <c r="F46" s="10"/>
     </row>
-    <row r="47" customFormat="false" ht="67.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="69.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>106</v>
       </c>
@@ -2389,7 +2689,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9.6328125" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -2398,8 +2698,8 @@
   </cols>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.5375" bottom="0.5375" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="5" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;10&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;10Page &amp;P</oddFooter>

--- a/documents/Lifespans in the Bible.xlsx
+++ b/documents/Lifespans in the Bible.xlsx
@@ -838,10 +838,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0207398807324925"/>
-          <c:y val="0.00867388520200256"/>
-          <c:w val="0.972663465090506"/>
-          <c:h val="0.840319012690651"/>
+          <c:x val="0.0207404280022165"/>
+          <c:y val="0.00867439017290563"/>
+          <c:w val="0.972636356439824"/>
+          <c:h val="0.840251499097631"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -1225,11 +1225,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="36003860"/>
-        <c:axId val="90724175"/>
+        <c:axId val="92971190"/>
+        <c:axId val="92321057"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="36003860"/>
+        <c:axId val="92971190"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1262,7 +1262,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90724175"/>
+        <c:crossAx val="92321057"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1270,7 +1270,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="90724175"/>
+        <c:axId val="92321057"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1321,7 +1321,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36003860"/>
+        <c:crossAx val="92971190"/>
         <c:crossesAt val="1"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="50"/>
@@ -1359,9 +1359,11 @@
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
+    <cs:lineWidthScale>1</cs:lineWidthScale>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor"/>
+    <a:defRPr sz="1800" b="0"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -1576,9 +1578,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>666000</xdr:colOff>
+      <xdr:colOff>665640</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>29520</xdr:rowOff>
+      <xdr:rowOff>29160</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1587,7 +1589,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="38160" y="23040"/>
-        <a:ext cx="13642920" cy="6183720"/>
+        <a:ext cx="13642560" cy="6183360"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2466,7 +2468,7 @@
       <c r="D33" s="10"/>
       <c r="F33" s="10"/>
     </row>
-    <row r="34" customFormat="false" ht="69.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>80</v>
       </c>
@@ -2479,7 +2481,7 @@
       <c r="D34" s="10"/>
       <c r="F34" s="10"/>
     </row>
-    <row r="35" customFormat="false" ht="69.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>82</v>
       </c>
@@ -2505,7 +2507,7 @@
       <c r="D36" s="10"/>
       <c r="F36" s="10"/>
     </row>
-    <row r="37" customFormat="false" ht="27.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>86</v>
       </c>
@@ -2518,7 +2520,7 @@
       <c r="D37" s="10"/>
       <c r="F37" s="10"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>88</v>
       </c>
@@ -2531,7 +2533,7 @@
       <c r="D38" s="10"/>
       <c r="F38" s="10"/>
     </row>
-    <row r="39" customFormat="false" ht="69.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>90</v>
       </c>
@@ -2570,7 +2572,7 @@
       <c r="D41" s="10"/>
       <c r="F41" s="10"/>
     </row>
-    <row r="42" customFormat="false" ht="69.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>96</v>
       </c>
@@ -2583,7 +2585,7 @@
       <c r="D42" s="10"/>
       <c r="F42" s="10"/>
     </row>
-    <row r="43" customFormat="false" ht="69.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>98</v>
       </c>
@@ -2596,7 +2598,7 @@
       <c r="D43" s="10"/>
       <c r="F43" s="10"/>
     </row>
-    <row r="44" customFormat="false" ht="69.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>100</v>
       </c>
@@ -2622,7 +2624,7 @@
       <c r="D45" s="10"/>
       <c r="F45" s="10"/>
     </row>
-    <row r="46" customFormat="false" ht="69.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>104</v>
       </c>
@@ -2635,7 +2637,7 @@
       <c r="D46" s="10"/>
       <c r="F46" s="10"/>
     </row>
-    <row r="47" customFormat="false" ht="69.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>106</v>
       </c>

--- a/documents/Lifespans in the Bible.xlsx
+++ b/documents/Lifespans in the Bible.xlsx
@@ -838,10 +838,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0207404280022165"/>
-          <c:y val="0.00867439017290563"/>
-          <c:w val="0.972636356439824"/>
-          <c:h val="0.840251499097631"/>
+          <c:x val="0.0207409753008233"/>
+          <c:y val="0.00867489520260829"/>
+          <c:w val="0.972609246358455"/>
+          <c:h val="0.840183977643223"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -1225,11 +1225,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="92971190"/>
-        <c:axId val="92321057"/>
+        <c:axId val="65730513"/>
+        <c:axId val="42881594"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="92971190"/>
+        <c:axId val="65730513"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1262,7 +1262,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92321057"/>
+        <c:crossAx val="42881594"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1270,7 +1270,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="92321057"/>
+        <c:axId val="42881594"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1321,7 +1321,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92971190"/>
+        <c:crossAx val="65730513"/>
         <c:crossesAt val="1"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="50"/>
@@ -1578,9 +1578,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>665640</xdr:colOff>
+      <xdr:colOff>665280</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>29160</xdr:rowOff>
+      <xdr:rowOff>28800</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1589,7 +1589,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="38160" y="23040"/>
-        <a:ext cx="13642560" cy="6183360"/>
+        <a:ext cx="13642200" cy="6183000"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
